--- a/exports/trend_1d/POWERINDIA_full_report.xlsx
+++ b/exports/trend_1d/POWERINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.09</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H2" t="n">
-        <v>954.35</v>
+        <v>917.25</v>
       </c>
       <c r="I2" t="n">
         <v>938.5446495425218</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K2" t="n">
-        <v>20.5</v>
+        <v>15.81</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>19.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44160</v>
+        <v>44161</v>
       </c>
       <c r="H3" t="n">
-        <v>980.95</v>
+        <v>1055.05</v>
       </c>
       <c r="I3" t="n">
         <v>1018.40754506756</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.94</v>
+        <v>-15.02</v>
       </c>
       <c r="L3" t="n">
-        <v>14.36</v>
+        <v>17.09</v>
       </c>
       <c r="M3" t="n">
         <v>3.64</v>
       </c>
       <c r="N3" t="n">
-        <v>5.13</v>
+        <v>7.55</v>
       </c>
       <c r="O3" t="n">
         <v>-3.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>16.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44263</v>
+        <v>44264</v>
       </c>
       <c r="H4" t="n">
-        <v>1396.8</v>
+        <v>1370.65</v>
       </c>
       <c r="I4" t="n">
         <v>1376.908282408904</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K4" t="n">
-        <v>32.39</v>
+        <v>29.91</v>
       </c>
       <c r="L4" t="n">
         <v>8.77</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>16.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H5" t="n">
-        <v>1426.85</v>
+        <v>1489.3</v>
       </c>
       <c r="I5" t="n">
         <v>1470.728840402263</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.1</v>
+        <v>-8.66</v>
       </c>
       <c r="L5" t="n">
-        <v>5.06</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>2.77</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44421</v>
+        <v>44424</v>
       </c>
       <c r="H6" t="n">
-        <v>1798.25</v>
+        <v>1778.5</v>
       </c>
       <c r="I6" t="n">
         <v>1791.865602634743</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K6" t="n">
-        <v>20.74</v>
+        <v>19.42</v>
       </c>
       <c r="L6" t="n">
         <v>5.11</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>14.44</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44433</v>
+        <v>44434</v>
       </c>
       <c r="H7" t="n">
-        <v>1959.7</v>
+        <v>2159.4</v>
       </c>
       <c r="I7" t="n">
         <v>2035.332975351493</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.19</v>
+        <v>-21.42</v>
       </c>
       <c r="L7" t="n">
-        <v>11.33</v>
+        <v>24.82</v>
       </c>
       <c r="M7" t="n">
         <v>2.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>10.19</v>
       </c>
       <c r="O7" t="n">
         <v>-1.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>19.02</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H8" t="n">
-        <v>2290.75</v>
+        <v>2249.2</v>
       </c>
       <c r="I8" t="n">
         <v>2279.544356753167</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" t="n">
-        <v>6.08</v>
+        <v>4.16</v>
       </c>
       <c r="L8" t="n">
         <v>10.41</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>19.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H9" t="n">
-        <v>2575.55</v>
+        <v>2629.45</v>
       </c>
       <c r="I9" t="n">
         <v>2603.331072050438</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-14.51</v>
+        <v>-16.91</v>
       </c>
       <c r="L9" t="n">
-        <v>15.6</v>
+        <v>17.24</v>
       </c>
       <c r="M9" t="n">
         <v>1.15</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H10" t="n">
-        <v>3089.25</v>
+        <v>2879.75</v>
       </c>
       <c r="I10" t="n">
         <v>3080.178639375174</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K10" t="n">
-        <v>17.49</v>
+        <v>9.52</v>
       </c>
       <c r="L10" t="n">
         <v>9.49</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>17.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H11" t="n">
-        <v>3253.1</v>
+        <v>3340.9</v>
       </c>
       <c r="I11" t="n">
         <v>3297.5942935404</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.96</v>
+        <v>-16.01</v>
       </c>
       <c r="L11" t="n">
-        <v>14.42</v>
+        <v>16.74</v>
       </c>
       <c r="M11" t="n">
-        <v>1.47</v>
+        <v>2.84</v>
       </c>
       <c r="N11" t="n">
         <v>5.88</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H12" t="n">
-        <v>3148.4</v>
+        <v>2876.45</v>
       </c>
       <c r="I12" t="n">
         <v>3095.362537772857</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.76</v>
+        <v>-13.9</v>
       </c>
       <c r="L12" t="n">
-        <v>8.58</v>
+        <v>14.66</v>
       </c>
       <c r="M12" t="n">
         <v>1.22</v>
       </c>
       <c r="N12" t="n">
-        <v>5.22</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>2.7</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>20.49</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H13" t="n">
-        <v>3274.45</v>
+        <v>3470</v>
       </c>
       <c r="I13" t="n">
         <v>3465.973451898422</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-13.84</v>
+        <v>-20.63</v>
       </c>
       <c r="L13" t="n">
-        <v>17.93</v>
+        <v>22.13</v>
       </c>
       <c r="M13" t="n">
         <v>1.64</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>12.87</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H14" t="n">
-        <v>3377.7</v>
+        <v>3170.2</v>
       </c>
       <c r="I14" t="n">
         <v>3267.523090452524</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.66</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>5.62</v>
+        <v>9.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0.91</v>
+        <v>1.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>6.14</v>
       </c>
       <c r="O14" t="n">
         <v>5.97</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44792</v>
+        <v>44795</v>
       </c>
       <c r="H15" t="n">
-        <v>3435.95</v>
+        <v>3536.85</v>
       </c>
       <c r="I15" t="n">
         <v>3526.974368068689</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.380000000000001</v>
+        <v>-11.57</v>
       </c>
       <c r="L15" t="n">
-        <v>11.98</v>
+        <v>16.08</v>
       </c>
       <c r="M15" t="n">
         <v>1.33</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H16" t="n">
-        <v>3369.1</v>
+        <v>3337.9</v>
       </c>
       <c r="I16" t="n">
         <v>3368.221075471243</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.74</v>
+        <v>-5.63</v>
       </c>
       <c r="L16" t="n">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="n">
         <v>4.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44904</v>
+        <v>44907</v>
       </c>
       <c r="H17" t="n">
-        <v>3077.25</v>
+        <v>3298.1</v>
       </c>
       <c r="I17" t="n">
         <v>3127.429299624148</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>7.81</v>
+        <v>1.19</v>
       </c>
       <c r="L17" t="n">
         <v>2.76</v>
@@ -1410,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>7.18</v>
       </c>
       <c r="O17" t="n">
         <v>-0.93</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>12.25</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H18" t="n">
-        <v>3121.65</v>
+        <v>3018.55</v>
       </c>
       <c r="I18" t="n">
         <v>3080.7265311998</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.35</v>
+        <v>-8.48</v>
       </c>
       <c r="L18" t="n">
-        <v>8.84</v>
+        <v>10.07</v>
       </c>
       <c r="M18" t="n">
         <v>1.61</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>7.18</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.87</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H19" t="n">
-        <v>3274.2</v>
+        <v>3313.25</v>
       </c>
       <c r="I19" t="n">
         <v>3283.84223091042</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.76</v>
       </c>
       <c r="L19" t="n">
-        <v>11.01</v>
+        <v>15.09</v>
       </c>
       <c r="M19" t="n">
         <v>0.53</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H20" t="n">
-        <v>3333.6</v>
+        <v>3146.65</v>
       </c>
       <c r="I20" t="n">
         <v>3189.478498792873</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>0.61</v>
+        <v>-5.03</v>
       </c>
       <c r="L20" t="n">
-        <v>3.08</v>
+        <v>6.1</v>
       </c>
       <c r="M20" t="n">
         <v>0.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>15.38</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45044</v>
+        <v>45048</v>
       </c>
       <c r="H21" t="n">
-        <v>3308.5</v>
+        <v>3448.75</v>
       </c>
       <c r="I21" t="n">
         <v>3340.795047709668</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.14</v>
+        <v>-9.6</v>
       </c>
       <c r="L21" t="n">
-        <v>7.92</v>
+        <v>10.28</v>
       </c>
       <c r="M21" t="n">
         <v>0.72</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45194</v>
+        <v>45195</v>
       </c>
       <c r="H22" t="n">
-        <v>4183.55</v>
+        <v>4130</v>
       </c>
       <c r="I22" t="n">
         <v>4156.761400073318</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K22" t="n">
-        <v>21.31</v>
+        <v>19.75</v>
       </c>
       <c r="L22" t="n">
         <v>4.02</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.33</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45210</v>
+        <v>45211</v>
       </c>
       <c r="H23" t="n">
-        <v>4117.35</v>
+        <v>4317.1</v>
       </c>
       <c r="I23" t="n">
         <v>4314.827716594632</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>0.31</v>
+        <v>-4.53</v>
       </c>
       <c r="L23" t="n">
-        <v>2.66</v>
+        <v>5.16</v>
       </c>
       <c r="M23" t="n">
         <v>0.53</v>
       </c>
       <c r="N23" t="n">
-        <v>2.67</v>
+        <v>4.85</v>
       </c>
       <c r="O23" t="n">
         <v>-1.28</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>11.22</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H24" t="n">
-        <v>4282.05</v>
+        <v>4155.35</v>
       </c>
       <c r="I24" t="n">
         <v>4197.027731898339</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>4.68</v>
+        <v>6.64</v>
       </c>
       <c r="M24" t="n">
         <v>0.4</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>11.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H25" t="n">
-        <v>4577</v>
+        <v>4595.1</v>
       </c>
       <c r="I25" t="n">
         <v>4591.298825762844</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>-10.15</v>
+        <v>-10.58</v>
       </c>
       <c r="L25" t="n">
-        <v>12.51</v>
+        <v>12.63</v>
       </c>
       <c r="M25" t="n">
         <v>2.16</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H26" t="n">
-        <v>12055.5</v>
+        <v>11828.55</v>
       </c>
       <c r="I26" t="n">
         <v>11834.42793345482</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K26" t="n">
-        <v>162.36</v>
+        <v>157.42</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>19.88</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H27" t="n">
-        <v>12308.35</v>
+        <v>12822.85</v>
       </c>
       <c r="I27" t="n">
         <v>12746.32327568387</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.06</v>
+        <v>-8.41</v>
       </c>
       <c r="L27" t="n">
-        <v>7.15</v>
+        <v>9.06</v>
       </c>
       <c r="M27" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
         <v>6.76</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.28</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H28" t="n">
-        <v>13880.55</v>
+        <v>13744.1</v>
       </c>
       <c r="I28" t="n">
         <v>13821.5576429742</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>8.25</v>
+        <v>7.18</v>
       </c>
       <c r="L28" t="n">
         <v>3.22</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>18.72</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H29" t="n">
-        <v>13589.6</v>
+        <v>14030.95</v>
       </c>
       <c r="I29" t="n">
         <v>13681.14351909207</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K29" t="n">
-        <v>1.12</v>
+        <v>-2.09</v>
       </c>
       <c r="L29" t="n">
         <v>8.74</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>14.03</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H30" t="n">
-        <v>13436.35</v>
+        <v>12724.05</v>
       </c>
       <c r="I30" t="n">
         <v>13317.72597977655</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.24</v>
+        <v>-9.31</v>
       </c>
       <c r="L30" t="n">
-        <v>5.82</v>
+        <v>10.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
         <v>3.25</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>18.26</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H31" t="n">
-        <v>12277.5</v>
+        <v>12863.55</v>
       </c>
       <c r="I31" t="n">
         <v>12406.00872869166</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>3.51</v>
+        <v>-1.1</v>
       </c>
       <c r="L31" t="n">
-        <v>7.2</v>
+        <v>15.32</v>
       </c>
       <c r="M31" t="n">
         <v>11.85</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>22.07</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H32" t="n">
-        <v>17534</v>
+        <v>17034</v>
       </c>
       <c r="I32" t="n">
         <v>17456.75214512806</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K32" t="n">
-        <v>36.31</v>
+        <v>32.42</v>
       </c>
       <c r="L32" t="n">
         <v>19.93</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>16.36</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H33" t="n">
-        <v>19441</v>
+        <v>19942</v>
       </c>
       <c r="I33" t="n">
         <v>19820.947969241</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>-14.13</v>
+        <v>-17.07</v>
       </c>
       <c r="L33" t="n">
-        <v>16.76</v>
+        <v>18.71</v>
       </c>
       <c r="M33" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="N33" t="n">
         <v>6.05</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.51</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="H34" t="n">
-        <v>19247</v>
+        <v>18001</v>
       </c>
       <c r="I34" t="n">
         <v>18426.9629333718</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.49</v>
+        <v>-9.73</v>
       </c>
       <c r="L34" t="n">
-        <v>8.029999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>4.65</v>
+        <v>6.47</v>
       </c>
       <c r="O34" t="n">
         <v>2.58</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>15.62</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H35" t="n">
-        <v>17919</v>
+        <v>20457</v>
       </c>
       <c r="I35" t="n">
         <v>18279.4831338153</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.46</v>
+        <v>-13.64</v>
       </c>
       <c r="L35" t="n">
-        <v>7.38</v>
+        <v>14.65</v>
       </c>
       <c r="M35" t="n">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>14.16</v>
       </c>
       <c r="O35" t="n">
         <v>-6.47</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.45</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H36" t="n">
-        <v>21850</v>
+        <v>20085</v>
       </c>
       <c r="I36" t="n">
         <v>20616.60333157842</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>6.81</v>
+        <v>-1.82</v>
       </c>
       <c r="L36" t="n">
         <v>8.74</v>
@@ -2493,7 +2924,7 @@
         <v>0.93</v>
       </c>
       <c r="N36" t="n">
-        <v>3.98</v>
+        <v>8.08</v>
       </c>
       <c r="O36" t="n">
         <v>14.16</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.77</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H37" t="n">
-        <v>18322</v>
+        <v>18862</v>
       </c>
       <c r="I37" t="n">
         <v>18609.10617350171</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="n">
-        <v>8.779999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="L37" t="n">
         <v>8.56</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.38</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H38" t="n">
-        <v>34610</v>
+        <v>33265</v>
       </c>
       <c r="I38" t="n">
         <v>33274.17988948173</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K38" t="n">
-        <v>83.48999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="L38" t="n">
         <v>5.37</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>16.7</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="H39" t="n">
-        <v>32600</v>
+        <v>36050</v>
       </c>
       <c r="I39" t="n">
         <v>34506.14368065061</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>12.24</v>
       </c>
       <c r="M39" t="n">
-        <v>2.08</v>
+        <v>7.36</v>
       </c>
       <c r="N39" t="n">
-        <v>4.59</v>
+        <v>10.58</v>
       </c>
       <c r="O39" t="n">
         <v>-3.89</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.85</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="H40" t="n">
-        <v>32200</v>
+        <v>32000</v>
       </c>
       <c r="I40" t="n">
         <v>32116.12025628258</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.68</v>
+        <v>-11.23</v>
       </c>
       <c r="L40" t="n">
         <v>11.93</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2781,6 +3272,14 @@
       <c r="Q41" t="n">
         <v>37</v>
       </c>
+      <c r="R41" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5631,7 +6130,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="6">
@@ -5641,7 +6140,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -5651,7 +6150,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8">
@@ -5661,7 +6160,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5671,7 +6170,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -5681,7 +6180,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131.4</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="11">
@@ -5691,7 +6190,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -5701,7 +6200,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -5711,7 +6210,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46.2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -5721,7 +6220,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.43</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="15">
@@ -5731,7 +6230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.93</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="16">
@@ -5741,7 +6240,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-4.68</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="17">
@@ -5751,7 +6250,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>162.36</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="18">
@@ -5761,7 +6260,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.7</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="19">
@@ -5771,7 +6270,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.57</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="20">
@@ -5781,7 +6280,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.56</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="21">
@@ -5791,7 +6290,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.93</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="22">
@@ -5801,7 +6300,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -5811,7 +6310,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -5821,7 +6320,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.64</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="25">
@@ -5841,7 +6340,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.91</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="27">
@@ -5861,7 +6360,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
